--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1034"/>
+  <dimension ref="A1:Z1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60596,14 +60596,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 2911-2024</t>
+          <t>A 2912-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -60653,14 +60653,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 2912-2024</t>
+          <t>A 2911-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60673,7 +60673,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60881,14 +60881,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 3877-2024</t>
+          <t>A 3859-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -60938,14 +60938,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 3859-2024</t>
+          <t>A 3871-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -60995,14 +60995,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 3871-2024</t>
+          <t>A 3877-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61391,7 +61391,7 @@
       </c>
       <c r="R1033" s="2" t="inlineStr"/>
     </row>
-    <row r="1034">
+    <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
           <t>A 5416-2024</t>
@@ -61401,7 +61401,7 @@
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61447,6 +61447,63 @@
         <v>0</v>
       </c>
       <c r="R1034" s="2" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>A 6188-2024</t>
+        </is>
+      </c>
+      <c r="B1035" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1035" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>OVANÅKER</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1035" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1035"/>
+  <dimension ref="A1:Z1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60710,14 +60710,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 3333-2024</t>
+          <t>A 3324-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -60767,14 +60767,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 3324-2024</t>
+          <t>A 3333-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
       </c>
       <c r="R1034" s="2" t="inlineStr"/>
     </row>
-    <row r="1035">
+    <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
           <t>A 6188-2024</t>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61504,6 +61504,63 @@
         <v>0</v>
       </c>
       <c r="R1035" s="2" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>A 6331-2024</t>
+        </is>
+      </c>
+      <c r="B1036" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C1036" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>OVANÅKER</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1036" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1036"/>
+  <dimension ref="A1:Z1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61337,14 +61337,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 5309-2024</t>
+          <t>A 5416-2024</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61357,7 +61357,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -61394,14 +61394,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 5416-2024</t>
+          <t>A 5309-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
       </c>
       <c r="R1035" s="2" t="inlineStr"/>
     </row>
-    <row r="1036">
+    <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
           <t>A 6331-2024</t>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61561,6 +61561,63 @@
         <v>0</v>
       </c>
       <c r="R1036" s="2" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>A 6761-2024</t>
+        </is>
+      </c>
+      <c r="B1037" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C1037" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>OVANÅKER</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1037" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60710,14 +60710,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 3324-2024</t>
+          <t>A 3333-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -60767,14 +60767,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 3333-2024</t>
+          <t>A 3324-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61337,14 +61337,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 5416-2024</t>
+          <t>A 5309-2024</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61357,7 +61357,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -61394,14 +61394,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 5309-2024</t>
+          <t>A 5416-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1037"/>
+  <dimension ref="A1:Z1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
       </c>
       <c r="R1036" s="2" t="inlineStr"/>
     </row>
-    <row r="1037">
+    <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
           <t>A 6761-2024</t>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61618,6 +61618,63 @@
         <v>0</v>
       </c>
       <c r="R1037" s="2" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>A 7135-2024</t>
+        </is>
+      </c>
+      <c r="B1038" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C1038" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>OVANÅKER</t>
+        </is>
+      </c>
+      <c r="G1038" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1038" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60710,14 +60710,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 3333-2024</t>
+          <t>A 3324-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -60767,14 +60767,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 3324-2024</t>
+          <t>A 3333-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60938,14 +60938,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 3871-2024</t>
+          <t>A 3877-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -60995,14 +60995,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 3877-2024</t>
+          <t>A 3871-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61337,14 +61337,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 5309-2024</t>
+          <t>A 5416-2024</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61357,7 +61357,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -61394,14 +61394,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 5416-2024</t>
+          <t>A 5309-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45344</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60881,14 +60881,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 3859-2024</t>
+          <t>A 3877-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -60938,14 +60938,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 3877-2024</t>
+          <t>A 3871-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -60995,14 +60995,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 3871-2024</t>
+          <t>A 3859-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61337,14 +61337,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 5416-2024</t>
+          <t>A 5309-2024</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61357,7 +61357,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -61394,14 +61394,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 5309-2024</t>
+          <t>A 5416-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45344</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60881,14 +60881,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 3877-2024</t>
+          <t>A 3871-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -60938,14 +60938,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 3871-2024</t>
+          <t>A 3859-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -60995,14 +60995,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 3859-2024</t>
+          <t>A 3877-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61015,7 +61015,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45344</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45217</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45217</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45217</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45217</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45217</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45217</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45217</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45217</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45217</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45217</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45218</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45217</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>45217</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45217</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45217</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45218</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45219</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45223</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45223</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45223</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45223</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45223</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45223</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45224</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45224</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45224</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45225</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45225</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45230</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45230</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56251,7 +56251,7 @@
         <v>45230</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45230</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>45230</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45231</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45231</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45231</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45231</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45233</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45237</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45237</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45238</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45238</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45238</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45238</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45239</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45240</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45240</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45240</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45243</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45244</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45244</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45251</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45252</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45253</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>45253</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45254</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45257</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>45257</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>45257</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45257</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45257</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45258</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45260</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45265</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45265</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45265</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>45265</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45265</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>45265</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45267</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45267</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45267</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45267</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45268</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45271</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45275</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45280</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45280</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45280</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45281</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45281</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45282</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45287</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45300</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>45300</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45300</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45301</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>45302</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59852,7 +59852,7 @@
         <v>45302</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45303</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45303</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45306</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60085,7 +60085,7 @@
         <v>45306</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>45306</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>45306</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45306</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45306</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60370,7 +60370,7 @@
         <v>45307</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>45308</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>45308</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45310</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45315</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45315</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45317</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45317</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45320</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60881,14 +60881,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 3871-2024</t>
+          <t>A 3859-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -60938,14 +60938,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 3859-2024</t>
+          <t>A 3871-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -61002,7 +61002,7 @@
         <v>45322</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45323</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45324</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45328</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45329</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         <v>45330</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>45331</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45331</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>45337</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45338</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45342</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45344</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>

--- a/Översikt OVANÅKER.xlsx
+++ b/Översikt OVANÅKER.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1038"/>
+  <dimension ref="A1:Z1040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43847</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>43616</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         <v>44819</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>43713</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44887</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>43616</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44320</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>43713</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>45177</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45302</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>45323</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>43349</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>43521</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>43875</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44362</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44362</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>44365</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44379</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>44463</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>44792</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44792</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45058</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>45154</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45210</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45280</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45302</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>43318</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>43320</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>43349</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>43349</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>43382</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>43392</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>43392</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>43402</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>43403</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>43409</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>43409</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>43409</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>43410</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>43412</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>43412</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>43416</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>43416</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>43419</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43419</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>43419</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43430</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>43434</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>43444</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>43444</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>43451</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43451</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>43451</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>43451</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>43451</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>43454</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>43454</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>43462</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43462</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43467</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>43479</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>43480</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>43481</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>43487</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>43493</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>43503</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>43504</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>43507</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43515</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43521</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43521</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43525</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43531</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43539</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43542</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43545</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43556</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43556</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43570</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43571</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43572</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43581</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43591</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43607</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43608</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43609</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43614</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>43614</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>43614</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>43616</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>43616</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>43616</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43616</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>43616</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>43616</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>43619</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>43619</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>43621</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>43621</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>43629</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>43629</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43640</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>43640</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>43641</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>43643</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>43671</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>43679</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>43679</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>43682</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43686</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43689</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43689</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>43690</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>43692</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>43692</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>43693</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>43697</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>43699</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>43700</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>43704</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>43705</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>43713</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>43718</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>43725</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>43725</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>43725</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>43726</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>43727</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43728</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43728</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>43731</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43731</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43731</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>43731</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>43731</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>43731</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>43735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>43739</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>43740</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>43747</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>43748</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>43749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>43755</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>43755</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>43763</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>43766</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>43774</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>43780</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>43780</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>43782</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>43787</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43788</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43788</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43790</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43790</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>43790</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>43790</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>43790</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>43796</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>43797</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>43802</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>43809</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>43812</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>43817</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>43818</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>43839</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>43846</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>43846</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>43846</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>43846</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>43846</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43847</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43850</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43852</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43852</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>43854</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43854</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>43854</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>43854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>43859</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>43874</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>43874</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>43874</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>43875</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>43881</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>43886</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>43888</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>43892</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>43893</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>43900</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>43903</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>43906</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>43907</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>43909</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>43910</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>43914</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>43914</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43915</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>43915</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43916</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43916</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43916</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>43917</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43917</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43917</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43917</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43917</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43921</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43921</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43922</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>43924</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>43924</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>43935</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>43935</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43936</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43937</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43937</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43942</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43942</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43945</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43948</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43949</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43950</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43951</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43957</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43957</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43962</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43965</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43965</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43969</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43985</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>43987</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43987</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43992</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43994</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43999</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44005</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44005</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44005</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44007</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44012</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44012</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44014</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44014</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>44021</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44025</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>44035</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>44041</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>44041</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44053</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44053</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44053</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44054</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44054</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44054</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44054</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>44061</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44062</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44063</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44063</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>44067</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44067</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44071</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>44083</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44083</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44089</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44091</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44091</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>44096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44096</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44102</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44103</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44105</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44106</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44109</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44109</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44109</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44112</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>44112</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44112</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44112</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>44113</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44116</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44120</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44131</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44131</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44131</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44137</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44137</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>44145</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>44145</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>44146</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44146</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44146</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44153</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44159</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44159</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44160</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44162</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44167</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44167</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44167</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44167</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44167</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44167</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44169</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44169</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44174</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44174</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44181</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44183</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44188</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44204</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44222</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44231</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44245</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44251</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44258</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44258</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44258</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44264</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44264</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44264</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44264</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44266</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44266</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44266</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44266</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44266</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44270</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44271</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44272</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44273</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44277</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44278</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>44279</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44285</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44298</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44298</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44301</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44305</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44310</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44310</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44312</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44313</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44314</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44314</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44314</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>44314</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44315</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44326</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44328</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44336</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44337</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44340</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44344</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44347</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44347</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44349</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44349</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44349</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44349</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44350</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44351</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44351</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44351</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44355</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44364</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44364</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44365</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44371</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>44371</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44376</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>44379</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44379</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44379</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>44379</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44379</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44379</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44379</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44379</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44382</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44384</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44384</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44384</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44389</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44400</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44400</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44425</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44425</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44425</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44425</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44427</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>44434</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44435</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44435</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44439</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>44445</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44447</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>44447</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>44463</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>44466</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44466</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>44470</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44470</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>44473</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44475</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44475</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44475</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>44475</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>44475</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44475</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44482</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44484</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44489</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44491</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44494</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44497</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>44497</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44503</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44503</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>44505</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>44512</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44516</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44517</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44517</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>44518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44523</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>44523</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44526</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44530</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>44530</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44531</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>44532</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>44536</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44537</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>44544</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44547</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>44564</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>44564</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44571</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44571</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44573</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44573</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44579</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44581</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44581</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44585</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44602</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44603</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44607</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44614</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44614</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44614</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44614</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44614</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44616</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44616</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44616</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44617</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44617</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44621</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44636</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44636</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44637</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44637</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44640</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44650</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44665</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44672</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44676</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44692</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44694</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>44694</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44698</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>44700</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44701</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>44705</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44705</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44705</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44706</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>44706</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44711</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44711</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44714</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44715</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44719</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44719</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44719</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44719</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44720</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44725</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44728</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44728</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>44729</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44729</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44732</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44732</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44740</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>44740</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>44746</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44749</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>44750</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44754</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44755</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44757</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44757</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44757</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44760</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>44760</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>44760</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>44770</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44774</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44774</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44776</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44776</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44785</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44789</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44790</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44797</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44798</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44798</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44800</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44800</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44799</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44802</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44804</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44805</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44811</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44812</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44818</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>44818</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44819</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44823</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44823</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44824</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44827</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44830</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44832</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44839</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44840</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44841</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44845</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44845</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44845</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44846</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44846</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44846</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44848</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44852</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44853</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>44853</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44855</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44858</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44859</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>44862</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44866</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44867</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44868</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44868</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44868</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44868</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44872</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44872</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44872</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44872</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44872</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44872</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44872</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>44874</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>44874</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44876</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44876</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>44879</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44879</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44880</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44880</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44881</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44883</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44883</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44883</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>44883</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44886</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>44886</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44886</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>44887</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>44889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>44889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44893</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>44894</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44897</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44900</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>44901</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>44902</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>44902</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44903</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44903</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44903</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44904</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44907</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>44909</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44910</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44910</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44911</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>44914</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>44914</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44915</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44917</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44922</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>44923</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44930</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44935</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44943</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44943</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>44943</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>44943</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>44946</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44949</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>44952</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>44956</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44956</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>44957</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>44957</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44957</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44958</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44959</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44959</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>44959</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44961</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>44961</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>44970</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>44977</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>44979</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>44985</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>44986</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>44986</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45000</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45002</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45002</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45002</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45002</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45005</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45009</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45009</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45020</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45033</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45033</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45035</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45036</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45036</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45036</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45036</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45037</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45040</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45044</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45044</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45050</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45050</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45051</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45054</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45056</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45067</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45068</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45068</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45069</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45070</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45070</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45070</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45071</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45072</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45072</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45079</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45079</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45079</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45079</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45079</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45086</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45086</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45091</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45091</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45092</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45092</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45092</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45092</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45096</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45096</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45096</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45096</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45102</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45102</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45103</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45103</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45103</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45103</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45106</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45111</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45112</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45113</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45113</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>45113</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45114</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45114</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45117</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45117</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45117</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45118</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45120</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45120</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45120</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>45120</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45127</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45127</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45133</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45133</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45139</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45145</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45149</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45149</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45149</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45149</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>45152</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45152</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45154</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45159</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45160</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45160</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45161</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45161</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45162</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45163</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45166</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45166</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45166</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45167</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45167</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45168</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45168</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45168</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45170</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45175</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45175</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45176</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45177</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45177</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45177</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45177</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45177</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45177</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>45181</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51661,7 +51661,7 @@
         <v>45182</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>45182</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>45183</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45183</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>45183</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>45183</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45183</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45188</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>45188</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>45188</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45189</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45190</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45195</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45196</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45196</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45201</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45201</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45205</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45205</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45205</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45205</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45210</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>45210</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45210</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45210</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45210</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45210</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45211</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45211</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45211</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45211</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45216</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45216</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>45216</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45216</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@